--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.72293474937896</v>
+        <v>1.904976896774081</v>
       </c>
       <c r="D2" t="n">
-        <v>42.51135530919821</v>
+        <v>6.908095237744709</v>
       </c>
       <c r="E2" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F2" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.65476011779671</v>
+        <v>6.443898519141965</v>
       </c>
       <c r="D3" t="n">
-        <v>60.80310680951</v>
+        <v>9.880504856545375</v>
       </c>
       <c r="E3" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F3" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.12022210629053</v>
+        <v>8.794536092272212</v>
       </c>
       <c r="D4" t="n">
-        <v>54.20652718733609</v>
+        <v>8.808560667942116</v>
       </c>
       <c r="E4" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F4" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.09333623539761</v>
+        <v>5.215167138252111</v>
       </c>
       <c r="D5" t="n">
-        <v>32.16542716373953</v>
+        <v>5.226881914107674</v>
       </c>
       <c r="E5" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F5" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.99308435154801</v>
+        <v>2.436376207126552</v>
       </c>
       <c r="D6" t="n">
-        <v>15.98145139813676</v>
+        <v>2.596985852197223</v>
       </c>
       <c r="E6" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F6" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.98285443837856</v>
+        <v>2.109713846236516</v>
       </c>
       <c r="D7" t="n">
-        <v>13.09503824160979</v>
+        <v>2.127943714261592</v>
       </c>
       <c r="E7" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F7" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.25266211288456</v>
+        <v>4.103557593343741</v>
       </c>
       <c r="D8" t="n">
-        <v>25.51976424619648</v>
+        <v>4.146961690006928</v>
       </c>
       <c r="E8" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F8" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>15.40403616284443</v>
+        <v>2.50315587646222</v>
       </c>
       <c r="D9" t="n">
-        <v>15.13132774283349</v>
+        <v>2.458840758210443</v>
       </c>
       <c r="E9" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F9" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.73607980413346</v>
+        <v>3.207112968171687</v>
       </c>
       <c r="D10" t="n">
-        <v>19.63110046282992</v>
+        <v>3.190053825209862</v>
       </c>
       <c r="E10" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F10" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.6568392743105</v>
+        <v>4.981736382075457</v>
       </c>
       <c r="D11" t="n">
-        <v>30.25455552045341</v>
+        <v>4.91636527207368</v>
       </c>
       <c r="E11" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F11" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>41.22245801170321</v>
+        <v>6.698649426901772</v>
       </c>
       <c r="D12" t="n">
-        <v>40.7753495706539</v>
+        <v>6.625994305231259</v>
       </c>
       <c r="E12" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F12" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>26.28516139991861</v>
+        <v>4.271338727486774</v>
       </c>
       <c r="D13" t="n">
-        <v>25.945191730717</v>
+        <v>4.216093656241513</v>
       </c>
       <c r="E13" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F13" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>52.92151425127818</v>
+        <v>8.599746065832704</v>
       </c>
       <c r="D14" t="n">
-        <v>45.51098768429443</v>
+        <v>7.395535498697845</v>
       </c>
       <c r="E14" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F14" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>49.00900015656846</v>
+        <v>7.963962525442375</v>
       </c>
       <c r="D15" t="n">
-        <v>48.57025478647671</v>
+        <v>7.892666402802465</v>
       </c>
       <c r="E15" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F15" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>16.59701790806134</v>
+        <v>2.697015410059968</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7071067811865476</v>
+        <v>0.114904851942814</v>
       </c>
       <c r="E16" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F16" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>15.15162848277377</v>
+        <v>2.462139628450738</v>
       </c>
       <c r="D17" t="n">
-        <v>14.77953439794438</v>
+        <v>2.401674339665962</v>
       </c>
       <c r="E17" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F17" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>8.972016110788598</v>
+        <v>1.457952618003147</v>
       </c>
       <c r="D18" t="n">
-        <v>5.756854437704164</v>
+        <v>0.9354888461269267</v>
       </c>
       <c r="E18" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F18" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>28.90578522579284</v>
+        <v>4.697190099191337</v>
       </c>
       <c r="D19" t="n">
-        <v>28.45877856446194</v>
+        <v>4.624551516725066</v>
       </c>
       <c r="E19" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F19" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>10.34552202619114</v>
+        <v>1.681147329256061</v>
       </c>
       <c r="D20" t="n">
-        <v>2.877112750272012</v>
+        <v>0.4675308219192019</v>
       </c>
       <c r="E20" t="n">
-        <v>14.34619353292824</v>
+        <v>2.331256449100839</v>
       </c>
       <c r="F20" t="n">
-        <v>17.07980718613467</v>
+        <v>2.775468667746884</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
